--- a/deliverables/qc_gap_analysis/tracker/CoQ_Retest_List_2026-09-18.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Retest_List_2026-09-18.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -18740,7 +18740,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
